--- a/lit_review_results/1-identification_phase/review_report/sok_literature_review_report_final_template.xlsx
+++ b/lit_review_results/1-identification_phase/review_report/sok_literature_review_report_final_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wolfrieder/PycharmProjects/sok_artifacts/lit_review_results/1-identification_phase/review_report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D388EC1E-94ED-454D-9D3D-2D2AABF04B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBA7940-8DEF-874E-889E-FE245CC33D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="940" windowWidth="35880" windowHeight="21320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
